--- a/Excel/MythConfig.xlsx
+++ b/Excel/MythConfig.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="123">
   <si>
     <t>ID</t>
   </si>
@@ -395,6 +395,15 @@
   </si>
   <si>
     <t>极戒*1，虚无精华</t>
+  </si>
+  <si>
+    <t>麒麟秘境</t>
+  </si>
+  <si>
+    <t>仙界秘境</t>
+  </si>
+  <si>
+    <t>神界秘境</t>
   </si>
 </sst>
 </file>
@@ -1367,7 +1376,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K51"/>
+  <dimension ref="A1:K54"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -2529,6 +2538,75 @@
         <v>119</v>
       </c>
     </row>
+    <row r="52" customHeight="1" spans="3:9">
+      <c r="C52" s="1">
+        <v>46</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E52" s="1">
+        <v>2</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="G52" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="H52" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="3:9">
+      <c r="C53" s="1">
+        <v>47</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E53" s="1">
+        <v>2</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="G53" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="H53" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="3:9">
+      <c r="C54" s="1">
+        <v>48</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E54" s="1">
+        <v>2</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="G54" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="H54" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E5" errorStyle="warning">

--- a/Excel/MythConfig.xlsx
+++ b/Excel/MythConfig.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="127">
   <si>
     <t>ID</t>
   </si>
@@ -404,6 +404,18 @@
   </si>
   <si>
     <t>神界秘境</t>
+  </si>
+  <si>
+    <t>魔域小鸡</t>
+  </si>
+  <si>
+    <t>10,2000,200,100,2000,50,15,20,10,10,1</t>
+  </si>
+  <si>
+    <t>魔域小鹿</t>
+  </si>
+  <si>
+    <t>魔域灵花</t>
   </si>
 </sst>
 </file>
@@ -1043,7 +1055,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1055,6 +1067,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
@@ -1376,7 +1389,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K54"/>
+  <dimension ref="A1:K58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -1477,13 +1490,13 @@
       <c r="E6" s="1">
         <v>1</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="9" t="s">
         <v>13</v>
       </c>
       <c r="K6" s="2">
@@ -1500,13 +1513,13 @@
       <c r="E7" s="1">
         <v>1</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="H7" s="9" t="s">
         <v>13</v>
       </c>
       <c r="K7" s="2">
@@ -1523,13 +1536,13 @@
       <c r="E8" s="1">
         <v>1</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="9" t="s">
         <v>16</v>
       </c>
       <c r="K8" s="2">
@@ -1546,13 +1559,13 @@
       <c r="E9" s="1">
         <v>1</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="9" t="s">
         <v>16</v>
       </c>
       <c r="K9" s="2">
@@ -1569,13 +1582,13 @@
       <c r="E10" s="1">
         <v>1</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="H10" s="9" t="s">
         <v>19</v>
       </c>
       <c r="K10" s="2">
@@ -1592,13 +1605,13 @@
       <c r="E11" s="1">
         <v>1</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="H11" s="8" t="s">
+      <c r="H11" s="9" t="s">
         <v>19</v>
       </c>
       <c r="K11" s="2">
@@ -1615,13 +1628,13 @@
       <c r="E12" s="1">
         <v>1</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="H12" s="8" t="s">
+      <c r="H12" s="9" t="s">
         <v>22</v>
       </c>
       <c r="K12" s="2">
@@ -1638,13 +1651,13 @@
       <c r="E13" s="1">
         <v>1</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="H13" s="8" t="s">
+      <c r="H13" s="9" t="s">
         <v>22</v>
       </c>
       <c r="K13" s="2">
@@ -1661,13 +1674,13 @@
       <c r="E14" s="1">
         <v>1</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="G14" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="H14" s="8" t="s">
+      <c r="H14" s="9" t="s">
         <v>25</v>
       </c>
       <c r="K14" s="2">
@@ -1684,13 +1697,13 @@
       <c r="E15" s="1">
         <v>1</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="G15" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="H15" s="8" t="s">
+      <c r="H15" s="9" t="s">
         <v>25</v>
       </c>
       <c r="K15" s="2">
@@ -1707,13 +1720,13 @@
       <c r="E16" s="1">
         <v>1</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="G16" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="H16" s="8" t="s">
+      <c r="H16" s="9" t="s">
         <v>28</v>
       </c>
       <c r="K16" s="2">
@@ -1730,13 +1743,13 @@
       <c r="E17" s="1">
         <v>1</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G17" s="7" t="s">
+      <c r="G17" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="H17" s="8" t="s">
+      <c r="H17" s="9" t="s">
         <v>28</v>
       </c>
       <c r="K17" s="2">
@@ -1753,13 +1766,13 @@
       <c r="E18" s="1">
         <v>1</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G18" s="7" t="s">
+      <c r="G18" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="H18" s="8" t="s">
+      <c r="H18" s="9" t="s">
         <v>31</v>
       </c>
       <c r="K18" s="2">
@@ -1776,13 +1789,13 @@
       <c r="E19" s="1">
         <v>1</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G19" s="7" t="s">
+      <c r="G19" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="H19" s="8" t="s">
+      <c r="H19" s="9" t="s">
         <v>31</v>
       </c>
       <c r="K19" s="2">
@@ -1799,13 +1812,13 @@
       <c r="E20" s="1">
         <v>1</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="F20" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G20" s="7" t="s">
+      <c r="G20" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="H20" s="8" t="s">
+      <c r="H20" s="9" t="s">
         <v>36</v>
       </c>
       <c r="K20" s="2">
@@ -1822,13 +1835,13 @@
       <c r="E21" s="1">
         <v>1</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="F21" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G21" s="7" t="s">
+      <c r="G21" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="H21" s="8" t="s">
+      <c r="H21" s="9" t="s">
         <v>36</v>
       </c>
       <c r="K21" s="2">
@@ -1845,13 +1858,13 @@
       <c r="E22" s="1">
         <v>1</v>
       </c>
-      <c r="F22" s="7" t="s">
+      <c r="F22" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="G22" s="7" t="s">
+      <c r="G22" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="H22" s="8" t="s">
+      <c r="H22" s="9" t="s">
         <v>41</v>
       </c>
       <c r="K22" s="2">
@@ -1868,13 +1881,13 @@
       <c r="E23" s="1">
         <v>1</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="F23" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="G23" s="7" t="s">
+      <c r="G23" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="H23" s="8" t="s">
+      <c r="H23" s="9" t="s">
         <v>41</v>
       </c>
       <c r="K23" s="2">
@@ -1891,13 +1904,13 @@
       <c r="E24" s="1">
         <v>1</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="F24" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="G24" s="7" t="s">
+      <c r="G24" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="H24" s="8" t="s">
+      <c r="H24" s="9" t="s">
         <v>41</v>
       </c>
       <c r="K24" s="2">
@@ -1914,13 +1927,13 @@
       <c r="E25" s="1">
         <v>1</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="F25" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="G25" s="7" t="s">
+      <c r="G25" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="H25" s="8" t="s">
+      <c r="H25" s="9" t="s">
         <v>49</v>
       </c>
       <c r="I25" s="2" t="s">
@@ -1940,13 +1953,13 @@
       <c r="E26" s="1">
         <v>1</v>
       </c>
-      <c r="F26" s="7" t="s">
+      <c r="F26" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="G26" s="7" t="s">
+      <c r="G26" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="H26" s="8" t="s">
+      <c r="H26" s="9" t="s">
         <v>54</v>
       </c>
       <c r="I26" s="2" t="s">
@@ -1966,13 +1979,13 @@
       <c r="E27" s="1">
         <v>1</v>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="F27" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="G27" s="7" t="s">
+      <c r="G27" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="H27" s="8" t="s">
+      <c r="H27" s="9" t="s">
         <v>58</v>
       </c>
       <c r="I27" s="2" t="s">
@@ -1992,13 +2005,13 @@
       <c r="E28" s="1">
         <v>1</v>
       </c>
-      <c r="F28" s="7" t="s">
+      <c r="F28" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="G28" s="7" t="s">
+      <c r="G28" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="H28" s="8" t="s">
+      <c r="H28" s="9" t="s">
         <v>61</v>
       </c>
       <c r="I28" s="2" t="s">
@@ -2018,13 +2031,13 @@
       <c r="E29" s="1">
         <v>1</v>
       </c>
-      <c r="F29" s="7" t="s">
+      <c r="F29" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="G29" s="7" t="s">
+      <c r="G29" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="H29" s="8" t="s">
+      <c r="H29" s="9" t="s">
         <v>63</v>
       </c>
       <c r="I29" s="2" t="s">
@@ -2047,13 +2060,13 @@
       <c r="E31" s="1">
         <v>2</v>
       </c>
-      <c r="F31" s="7" t="s">
+      <c r="F31" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="G31" s="7" t="s">
+      <c r="G31" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="H31" s="8" t="s">
+      <c r="H31" s="9" t="s">
         <v>66</v>
       </c>
       <c r="I31" s="2" t="s">
@@ -2073,13 +2086,13 @@
       <c r="E32" s="1">
         <v>2</v>
       </c>
-      <c r="F32" s="7" t="s">
+      <c r="F32" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="G32" s="7" t="s">
+      <c r="G32" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="H32" s="8" t="s">
+      <c r="H32" s="9" t="s">
         <v>66</v>
       </c>
       <c r="I32" s="2" t="s">
@@ -2099,13 +2112,13 @@
       <c r="E33" s="1">
         <v>2</v>
       </c>
-      <c r="F33" s="7" t="s">
+      <c r="F33" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="G33" s="7" t="s">
+      <c r="G33" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="H33" s="8" t="s">
+      <c r="H33" s="9" t="s">
         <v>66</v>
       </c>
       <c r="I33" s="2" t="s">
@@ -2125,13 +2138,13 @@
       <c r="E34" s="1">
         <v>2</v>
       </c>
-      <c r="F34" s="7" t="s">
+      <c r="F34" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="G34" s="7" t="s">
+      <c r="G34" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="H34" s="8" t="s">
+      <c r="H34" s="9" t="s">
         <v>66</v>
       </c>
       <c r="I34" s="2" t="s">
@@ -2151,13 +2164,13 @@
       <c r="E35" s="1">
         <v>2</v>
       </c>
-      <c r="F35" s="7" t="s">
+      <c r="F35" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="G35" s="7" t="s">
+      <c r="G35" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="H35" s="8" t="s">
+      <c r="H35" s="9" t="s">
         <v>66</v>
       </c>
       <c r="I35" s="2" t="s">
@@ -2177,13 +2190,13 @@
       <c r="E36" s="1">
         <v>2</v>
       </c>
-      <c r="F36" s="7" t="s">
+      <c r="F36" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="G36" s="7" t="s">
+      <c r="G36" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="H36" s="8" t="s">
+      <c r="H36" s="9" t="s">
         <v>66</v>
       </c>
       <c r="I36" s="2" t="s">
@@ -2203,13 +2216,13 @@
       <c r="E37" s="1">
         <v>2</v>
       </c>
-      <c r="F37" s="7" t="s">
+      <c r="F37" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="G37" s="7" t="s">
+      <c r="G37" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="H37" s="8" t="s">
+      <c r="H37" s="9" t="s">
         <v>81</v>
       </c>
       <c r="I37" s="2" t="s">
@@ -2226,13 +2239,13 @@
       <c r="E38" s="1">
         <v>2</v>
       </c>
-      <c r="F38" s="7" t="s">
+      <c r="F38" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="G38" s="7" t="s">
+      <c r="G38" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="H38" s="8" t="s">
+      <c r="H38" s="9" t="s">
         <v>81</v>
       </c>
       <c r="I38" s="2" t="s">
@@ -2249,13 +2262,13 @@
       <c r="E39" s="1">
         <v>2</v>
       </c>
-      <c r="F39" s="7" t="s">
+      <c r="F39" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="G39" s="7" t="s">
+      <c r="G39" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="H39" s="8" t="s">
+      <c r="H39" s="9" t="s">
         <v>81</v>
       </c>
       <c r="I39" s="2" t="s">
@@ -2272,13 +2285,13 @@
       <c r="E40" s="1">
         <v>2</v>
       </c>
-      <c r="F40" s="7" t="s">
+      <c r="F40" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="G40" s="7" t="s">
+      <c r="G40" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="H40" s="8" t="s">
+      <c r="H40" s="9" t="s">
         <v>92</v>
       </c>
       <c r="I40" s="2" t="s">
@@ -2295,13 +2308,13 @@
       <c r="E41" s="1">
         <v>2</v>
       </c>
-      <c r="F41" s="7" t="s">
+      <c r="F41" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="G41" s="7" t="s">
+      <c r="G41" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="H41" s="8" t="s">
+      <c r="H41" s="9" t="s">
         <v>81</v>
       </c>
       <c r="I41" s="2" t="s">
@@ -2318,13 +2331,13 @@
       <c r="E42" s="1">
         <v>2</v>
       </c>
-      <c r="F42" s="7" t="s">
+      <c r="F42" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="G42" s="7" t="s">
+      <c r="G42" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="H42" s="8" t="s">
+      <c r="H42" s="9" t="s">
         <v>81</v>
       </c>
       <c r="I42" s="2" t="s">
@@ -2341,13 +2354,13 @@
       <c r="E43" s="1">
         <v>2</v>
       </c>
-      <c r="F43" s="7" t="s">
+      <c r="F43" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="G43" s="7" t="s">
+      <c r="G43" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="H43" s="8" t="s">
+      <c r="H43" s="9" t="s">
         <v>81</v>
       </c>
       <c r="I43" s="2" t="s">
@@ -2364,13 +2377,13 @@
       <c r="E44" s="1">
         <v>2</v>
       </c>
-      <c r="F44" s="7" t="s">
+      <c r="F44" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="G44" s="7" t="s">
+      <c r="G44" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="H44" s="8" t="s">
+      <c r="H44" s="9" t="s">
         <v>92</v>
       </c>
       <c r="I44" s="2" t="s">
@@ -2387,13 +2400,13 @@
       <c r="E45" s="1">
         <v>2</v>
       </c>
-      <c r="F45" s="7" t="s">
+      <c r="F45" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="G45" s="7" t="s">
+      <c r="G45" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="H45" s="8" t="s">
+      <c r="H45" s="9" t="s">
         <v>81</v>
       </c>
       <c r="I45" s="2" t="s">
@@ -2410,13 +2423,13 @@
       <c r="E46" s="1">
         <v>2</v>
       </c>
-      <c r="F46" s="7" t="s">
+      <c r="F46" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="G46" s="7" t="s">
+      <c r="G46" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="H46" s="8" t="s">
+      <c r="H46" s="9" t="s">
         <v>81</v>
       </c>
       <c r="I46" s="2" t="s">
@@ -2433,13 +2446,13 @@
       <c r="E47" s="1">
         <v>2</v>
       </c>
-      <c r="F47" s="7" t="s">
+      <c r="F47" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="G47" s="7" t="s">
+      <c r="G47" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="H47" s="8" t="s">
+      <c r="H47" s="9" t="s">
         <v>81</v>
       </c>
       <c r="I47" s="2" t="s">
@@ -2456,13 +2469,13 @@
       <c r="E48" s="1">
         <v>2</v>
       </c>
-      <c r="F48" s="7" t="s">
+      <c r="F48" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="G48" s="7" t="s">
+      <c r="G48" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="H48" s="8" t="s">
+      <c r="H48" s="9" t="s">
         <v>81</v>
       </c>
       <c r="I48" s="2" t="s">
@@ -2479,13 +2492,13 @@
       <c r="E49" s="1">
         <v>2</v>
       </c>
-      <c r="F49" s="7" t="s">
+      <c r="F49" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="G49" s="7" t="s">
+      <c r="G49" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="H49" s="8" t="s">
+      <c r="H49" s="9" t="s">
         <v>81</v>
       </c>
       <c r="I49" s="2" t="s">
@@ -2502,13 +2515,13 @@
       <c r="E50" s="1">
         <v>2</v>
       </c>
-      <c r="F50" s="7" t="s">
+      <c r="F50" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="G50" s="7" t="s">
+      <c r="G50" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="H50" s="8" t="s">
+      <c r="H50" s="9" t="s">
         <v>81</v>
       </c>
       <c r="I50" s="2" t="s">
@@ -2525,13 +2538,13 @@
       <c r="E51" s="1">
         <v>2</v>
       </c>
-      <c r="F51" s="7" t="s">
+      <c r="F51" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="G51" s="7" t="s">
+      <c r="G51" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="H51" s="8" t="s">
+      <c r="H51" s="9" t="s">
         <v>81</v>
       </c>
       <c r="I51" s="2" t="s">
@@ -2548,13 +2561,13 @@
       <c r="E52" s="1">
         <v>2</v>
       </c>
-      <c r="F52" s="7" t="s">
+      <c r="F52" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="G52" s="7" t="s">
+      <c r="G52" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="H52" s="8" t="s">
+      <c r="H52" s="9" t="s">
         <v>81</v>
       </c>
       <c r="I52" s="2" t="s">
@@ -2571,13 +2584,13 @@
       <c r="E53" s="1">
         <v>2</v>
       </c>
-      <c r="F53" s="7" t="s">
+      <c r="F53" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="G53" s="7" t="s">
+      <c r="G53" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="H53" s="8" t="s">
+      <c r="H53" s="9" t="s">
         <v>92</v>
       </c>
       <c r="I53" s="2" t="s">
@@ -2594,17 +2607,86 @@
       <c r="E54" s="1">
         <v>2</v>
       </c>
-      <c r="F54" s="7" t="s">
+      <c r="F54" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="G54" s="7" t="s">
+      <c r="G54" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="H54" s="8" t="s">
+      <c r="H54" s="9" t="s">
         <v>81</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>107</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="3:9">
+      <c r="C56" s="1">
+        <v>49</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="E56" s="1">
+        <v>3</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="H56" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="3:9">
+      <c r="C57" s="1">
+        <v>50</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="E57" s="1">
+        <v>3</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G57" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="H57" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="3:9">
+      <c r="C58" s="1">
+        <v>51</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E58" s="1">
+        <v>3</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G58" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="H58" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>
